--- a/docs/import-templates/account-master-template.xlsx
+++ b/docs/import-templates/account-master-template.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="88">
   <si>
     <t>NMWC — ACCOUNT MASTER (organization) import</t>
   </si>
@@ -185,6 +185,12 @@
   </si>
   <si>
     <t>Set to "yes" to change an EXISTING user's role. (Cannot promote to/from MANAGER or STEWARD — use /users.)</t>
+  </si>
+  <si>
+    <t>must_change_password</t>
+  </si>
+  <si>
+    <t>Set to "yes" to force the person to choose a new password at first login. Only then is a short initial password (4+) accepted; the one they choose must be 12+.</t>
   </si>
   <si>
     <t>TIP: create MANAGER and STEWARD accounts in the app first (Users page), then this import can reference a manager as a salesman's supervisor if you use the management ladder.</t>
@@ -691,7 +697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1150,21 +1156,21 @@
     </row>
     <row r="33" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>1</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>1</v>
@@ -1178,7 +1184,7 @@
     </row>
     <row r="35" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>1</v>
@@ -1187,6 +1193,20 @@
         <v>1</v>
       </c>
       <c r="D35" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1214,18 +1234,18 @@
     </row>
     <row r="2" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:2" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1256,35 +1276,35 @@
     </row>
     <row r="2" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1295,7 +1315,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="14" customWidth="1"/>
@@ -1305,9 +1325,10 @@
     <col min="8" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
     <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="12" max="12" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="20" customHeight="1" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>26</v>
       </c>
@@ -1341,19 +1362,22 @@
       <c r="K1" s="5" t="s">
         <v>55</v>
       </c>
+      <c r="L1" s="5" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="2" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>1</v>
@@ -1379,22 +1403,22 @@
     </row>
     <row r="3" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>72</v>
-      </c>
       <c r="E3" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>1</v>
@@ -1414,16 +1438,16 @@
     </row>
     <row r="4" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>1</v>
@@ -1432,7 +1456,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>1</v>
@@ -1449,16 +1473,16 @@
     </row>
     <row r="5" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>1</v>
@@ -1484,16 +1508,16 @@
     </row>
     <row r="6" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>1</v>

--- a/docs/import-templates/account-master-template.xlsx
+++ b/docs/import-templates/account-master-template.xlsx
@@ -97,7 +97,7 @@
     <t>username</t>
   </si>
   <si>
-    <t>lowercase, 3–50, a–z 0–9 . _ -</t>
+    <t>lowercase, 1–50, a–z 0–9 . _ -</t>
   </si>
   <si>
     <t>Login name. Must be lowercase and unique.</t>

--- a/docs/import-templates/account-master-template.xlsx
+++ b/docs/import-templates/account-master-template.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="87">
   <si>
     <t>NMWC — ACCOUNT MASTER (organization) import</t>
   </si>
@@ -136,10 +136,10 @@
     <t>Required for SALESMAN</t>
   </si>
   <si>
-    <t>a username from this sheet</t>
-  </si>
-  <si>
-    <t>The salesman's supervisor. Blank on a re-import = keep the existing supervisor (does not unlink).</t>
+    <t>the username of an ACTIVE SUPERVISOR or MANAGER</t>
+  </si>
+  <si>
+    <t>The salesman's supervisor, on this sheet or already in the CRM. Anyone else (a salesman, viewer, approver or deactivated account) holds the row back, unless it is already this person's supervisor. Blank on a re-import = keep the existing supervisor (does not unlink).</t>
   </si>
   <si>
     <t>route_code</t>
@@ -157,10 +157,10 @@
     <t>Required for ACCOUNTANT</t>
   </si>
   <si>
-    <t>comma-separated Region codes, e.g. MCT,BAT</t>
-  </si>
-  <si>
-    <t>Regions this accountant covers — REQUIRED, else the accountant sees no approvals and the credit chain stalls. Ignored for other roles.</t>
+    <t>comma-separated Region codes, e.g. MCT</t>
+  </si>
+  <si>
+    <t>Regions this accountant covers — REQUIRED, else the accountant sees no approvals and the credit chain stalls. Go-live issues one accountant per region, so this is normally a SINGLE code. Also sets a MANAGER’s regions; ignored for every other role. An unknown code, or a value containing no region code, quarantines the row rather than silently clearing the account’s regions.</t>
   </si>
   <si>
     <t>email</t>
@@ -178,13 +178,13 @@
     <t>yes / blank</t>
   </si>
   <si>
-    <t>Set to "yes" to rotate an EXISTING user's password (also logs them out). Must also fill "password".</t>
+    <t>Set to "yes" to rotate an EXISTING user's password (also logs them out). Must also fill "password". It may not be their current password or one of their last five, and your own password cannot be reset here.</t>
   </si>
   <si>
     <t>change_role</t>
   </si>
   <si>
-    <t>Set to "yes" to change an EXISTING user's role. (Cannot promote to/from MANAGER or STEWARD — use /users.)</t>
+    <t>Set to "yes" to change an EXISTING user's role. (Cannot promote to/from MANAGER or STEWARD — use /users.) A SUPERVISOR with people reporting to them keeps the role until they are reassigned.</t>
   </si>
   <si>
     <t>must_change_password</t>
@@ -257,9 +257,6 @@
   </si>
   <si>
     <t>ACCOUNTANT</t>
-  </si>
-  <si>
-    <t>MCT,BAT</t>
   </si>
   <si>
     <t>faisal.finance</t>
@@ -1456,7 +1453,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>1</v>
@@ -1473,13 +1470,13 @@
     </row>
     <row r="5" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>83</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>84</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>74</v>
@@ -1508,13 +1505,13 @@
     </row>
     <row r="6" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C6" s="6" t="s">
         <v>86</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>87</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>74</v>

--- a/docs/import-templates/account-master-template.xlsx
+++ b/docs/import-templates/account-master-template.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="90">
   <si>
     <t>NMWC — ACCOUNT MASTER (organization) import</t>
   </si>
@@ -22,7 +22,7 @@
     <t/>
   </si>
   <si>
-    <t>PURPOSE: load your regions, routes, and people (salesmen, supervisors, accountants, finance managers, GM, viewers).</t>
+    <t>PURPOSE: load your regions, routes, and people (salesmen, supervisors, accountants, finance managers, GM, sales director, viewers).</t>
   </si>
   <si>
     <t>ORDER: import this file FIRST — before the Customer master. Inside the file the app auto-processes supervisors before salesmen, so you can keep everyone on one Users sheet.</t>
@@ -112,7 +112,7 @@
     <t>role</t>
   </si>
   <si>
-    <t>SALESMAN | SUPERVISOR | ACCOUNTANT | FINANCE_MANAGER | GM | VIEWER</t>
+    <t>SALESMAN | SUPERVISOR | ACCOUNTANT | FINANCE_MANAGER | GM | SALES_DIRECTOR | VIEWER</t>
   </si>
   <si>
     <t>MANAGER and STEWARD CANNOT be created here — create them in the app (/users) first, then load everyone else here.</t>
@@ -275,6 +275,15 @@
   </si>
   <si>
     <t>GM</t>
+  </si>
+  <si>
+    <t>sales.director</t>
+  </si>
+  <si>
+    <t>Sales Director Name</t>
+  </si>
+  <si>
+    <t>SALES_DIRECTOR</t>
   </si>
 </sst>
 </file>
@@ -1312,7 +1321,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="14" customWidth="1"/>
@@ -1538,6 +1547,41 @@
         <v>1</v>
       </c>
     </row>
+    <row r="7" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/docs/import-templates/account-master-template.xlsx
+++ b/docs/import-templates/account-master-template.xlsx
@@ -88,7 +88,7 @@
     <t>a code from the Regions sheet</t>
   </si>
   <si>
-    <t>Which region this route belongs to. Must exist in Regions.</t>
+    <t>Which region this route belongs to. Must exist in Regions. A route NEVER moves to another region: a row naming another region than the route has is held back (its name is still saved). Close the route and open a new one in the other region.</t>
   </si>
   <si>
     <t>SHEET: Users</t>
